--- a/Assets/Editor/ExcelData/PlayerData.xlsx
+++ b/Assets/Editor/ExcelData/PlayerData.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B5737F-CDF7-416F-A6F9-2DB88176B3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40C84A0-B6AD-407A-9134-BB9A9550206B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="WeaponData" sheetId="1" r:id="rId1"/>
+    <sheet name="PlayerData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,73 +39,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Range</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Melee</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>야구방망이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>총</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>폭탄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Throw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>weaponId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>weaponType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>weaponName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attackCooldawn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>range</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>playerId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxHp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dashSpeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dashCooldown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>player</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>prefabAddressable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iconAddressable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gun</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -490,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A09DDB1-B5FD-4E66-B653-801C3E995E61}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -498,94 +458,46 @@
     <col min="3" max="3" width="18.625" customWidth="1"/>
     <col min="4" max="4" width="16.3125" customWidth="1"/>
     <col min="5" max="5" width="17.75" customWidth="1"/>
+    <col min="6" max="6" width="24.5625" customWidth="1"/>
     <col min="7" max="7" width="28.8125" customWidth="1"/>
     <col min="8" max="8" width="43.3125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
       <c r="D2">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>1.5</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
         <v>4</v>
-      </c>
-      <c r="D4">
-        <v>30</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Editor/ExcelData/PlayerData.xlsx
+++ b/Assets/Editor/ExcelData/PlayerData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40C84A0-B6AD-407A-9134-BB9A9550206B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F90373-B3E9-4732-8DB1-3769E99A390F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>playerId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -66,6 +66,10 @@
   </si>
   <si>
     <t>prefabAddressable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dashDuration</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -450,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A09DDB1-B5FD-4E66-B653-801C3E995E61}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -463,7 +467,7 @@
     <col min="8" max="8" width="43.3125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,13 +481,16 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -497,11 +504,15 @@
         <v>20</v>
       </c>
       <c r="E2">
+        <v>0.3</v>
+      </c>
+      <c r="F2">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Editor/ExcelData/PlayerData.xlsx
+++ b/Assets/Editor/ExcelData/PlayerData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F90373-B3E9-4732-8DB1-3769E99A390F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F06D843-B57F-488D-8B07-DC318DEBA3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>playerId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,6 +71,9 @@
   <si>
     <t>dashDuration</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Characters/Player</t>
   </si>
 </sst>
 </file>
@@ -498,16 +501,19 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E2">
         <v>0.3</v>
       </c>
       <c r="F2">
         <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
